--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486708_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486708_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2696</v>
+        <v>5.8582</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0214</v>
+        <v>3.0074</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2481</v>
+        <v>2.8508</v>
       </c>
       <c r="G2" t="n">
         <v>3.2493</v>
@@ -610,13 +610,13 @@
         <v>2.3169</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6457000000000001</v>
+        <v>1.2344</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.745</v>
+        <v>0.241</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3907</v>
+        <v>0.9933999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>0.023</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.726</v>
+        <v>3.988</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7269</v>
+        <v>3.9889</v>
       </c>
       <c r="F3" t="n">
         <v>-0.0009</v>
@@ -688,10 +688,10 @@
         <v>1.3515</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7723</v>
+        <v>1.0343</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2204</v>
+        <v>0.4824</v>
       </c>
       <c r="U3" t="n">
         <v>0.5518999999999999</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. LUENGO NEVADO</t>
+          <t>D. GARCIA NAVARO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.219</v>
+        <v>2.7624</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8147</v>
+        <v>0.6839</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4043</v>
+        <v>2.0785</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2738</v>
+        <v>1.3682</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0003</v>
+        <v>-2.8479</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2735</v>
+        <v>4.2162</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3985</v>
+        <v>1.838</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2764</v>
+        <v>-1.9509</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1221</v>
+        <v>3.7889</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1247</v>
+        <v>-0.4698</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2761</v>
+        <v>-0.897</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1514</v>
+        <v>0.4272</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3515</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.8962</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3515</v>
+        <v>2.3169</v>
       </c>
       <c r="S4" t="n">
-        <v>1.528</v>
+        <v>0.7653</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1306</v>
+        <v>0.5996</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3974</v>
+        <v>0.1657</v>
       </c>
       <c r="V4" t="n">
+        <v>1.2081</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.1424</v>
+      </c>
+      <c r="X4" t="n">
         <v>0.06560000000000001</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.2856</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-0.22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. GARCIA NAVARO</t>
+          <t>C. LUENGO NEVADO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6698</v>
+        <v>2.5736</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9389999999999999</v>
+        <v>1.1942</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7309</v>
+        <v>1.3794</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3682</v>
+        <v>0.2738</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.8479</v>
+        <v>0.0003</v>
       </c>
       <c r="I5" t="n">
-        <v>4.2162</v>
+        <v>0.2735</v>
       </c>
       <c r="J5" t="n">
-        <v>1.838</v>
+        <v>0.3985</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.9509</v>
+        <v>0.2764</v>
       </c>
       <c r="L5" t="n">
-        <v>3.7889</v>
+        <v>0.1221</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4698</v>
+        <v>-0.1247</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.897</v>
+        <v>-0.2761</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4272</v>
+        <v>0.1514</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.5792</v>
+        <v>1.3515</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.8962</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3169</v>
+        <v>1.3515</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6727</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8547</v>
+        <v>0.51</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1819</v>
+        <v>0.3725</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2081</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1424</v>
+        <v>0.2856</v>
       </c>
       <c r="X5" t="n">
-        <v>0.06560000000000001</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2857</v>
+        <v>2.4691</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9305</v>
+        <v>2.0891</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3552</v>
+        <v>0.38</v>
       </c>
       <c r="G6" t="n">
         <v>0.8128</v>
@@ -922,13 +922,13 @@
         <v>0.9654</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8164</v>
+        <v>0.9998</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3859</v>
+        <v>0.5445</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4305</v>
+        <v>0.4553</v>
       </c>
       <c r="V6" t="n">
         <v>0.6565</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PARDO</t>
+          <t>S. HERTEL HERMOSA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6333</v>
+        <v>1.9809</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0507</v>
+        <v>3.1611</v>
       </c>
       <c r="F7" t="n">
-        <v>2.684</v>
+        <v>-1.1802</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6726</v>
+        <v>2.3989</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1798</v>
+        <v>0.448</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4928</v>
+        <v>1.9509</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2942</v>
+        <v>3.3308</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5595</v>
+        <v>0.7242</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7347</v>
+        <v>2.6066</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3783</v>
+        <v>-0.9319</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6203</v>
+        <v>-0.2763</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.242</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.9654</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9308</v>
+        <v>0.9654</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1049</v>
+        <v>-0.4413</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4142</v>
+        <v>-0.4553</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3093</v>
+        <v>0.014</v>
       </c>
       <c r="V7" t="n">
-        <v>0.06560000000000001</v>
+        <v>-0.9421</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X7" t="n">
-        <v>0.06560000000000001</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. GONZALEZ NOGALES</t>
+          <t>I. MARTINEZ PARDO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6016</v>
+        <v>1.7933</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7004</v>
+        <v>-0.9404</v>
       </c>
       <c r="F8" t="n">
-        <v>2.302</v>
+        <v>2.7337</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1136</v>
+        <v>1.6726</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3657</v>
+        <v>1.1798</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4793</v>
+        <v>0.4928</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9679</v>
+        <v>1.2942</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3237</v>
+        <v>0.5595</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6442</v>
+        <v>0.7347</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8542999999999999</v>
+        <v>0.3783</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6893</v>
+        <v>0.6203</v>
       </c>
       <c r="O8" t="n">
-        <v>0.165</v>
+        <v>-0.242</v>
       </c>
       <c r="P8" t="n">
-        <v>1.9308</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R8" t="n">
         <v>1.9308</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3752</v>
+        <v>0.0551</v>
       </c>
       <c r="T8" t="n">
         <v>-0.3038</v>
       </c>
       <c r="U8" t="n">
-        <v>0.679</v>
+        <v>0.3589</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5908</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5712</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.162</v>
+        <v>0.06560000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. HERTEL HERMOSA</t>
+          <t>J. GONZALEZ NOGALES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4899</v>
+        <v>1.385</v>
       </c>
       <c r="E9" t="n">
-        <v>2.8439</v>
+        <v>-0.6935</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.354</v>
+        <v>2.0785</v>
       </c>
       <c r="G9" t="n">
-        <v>2.3989</v>
+        <v>-0.1136</v>
       </c>
       <c r="H9" t="n">
-        <v>0.448</v>
+        <v>0.3657</v>
       </c>
       <c r="I9" t="n">
-        <v>1.9509</v>
+        <v>-0.4793</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3308</v>
+        <v>-0.9679</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7242</v>
+        <v>-0.3237</v>
       </c>
       <c r="L9" t="n">
-        <v>2.6066</v>
+        <v>-0.6442</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9319</v>
+        <v>0.8542999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2763</v>
+        <v>0.6893</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6556999999999999</v>
+        <v>0.165</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9654</v>
+        <v>1.9308</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9654</v>
+        <v>1.9308</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9323</v>
+        <v>0.1586</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7725</v>
+        <v>-0.2969</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1598</v>
+        <v>0.4555</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9421</v>
+        <v>-0.5908</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2856</v>
+        <v>0.5712</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2277</v>
+        <v>-1.162</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8699</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="E10" t="n">
         <v>0.7308</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1391</v>
+        <v>-0.0348</v>
       </c>
       <c r="G10" t="n">
         <v>0.1082</v>
@@ -1234,13 +1234,13 @@
         <v>0.3862</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1325</v>
+        <v>-0.0413</v>
       </c>
       <c r="T10" t="n">
         <v>-0.1655</v>
       </c>
       <c r="U10" t="n">
-        <v>0.298</v>
+        <v>0.1242</v>
       </c>
       <c r="V10" t="n">
         <v>0.243</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5203</v>
+        <v>0.4873</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3065</v>
+        <v>-2.5134</v>
       </c>
       <c r="F11" t="n">
-        <v>2.8269</v>
+        <v>3.0007</v>
       </c>
       <c r="G11" t="n">
         <v>-0.3953</v>
@@ -1312,13 +1312,13 @@
         <v>1.3515</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5295</v>
+        <v>0.4964</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1377</v>
+        <v>-0.0692</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3918</v>
+        <v>0.5656</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.7807</v>
+        <v>-2.782</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2892</v>
+        <v>-2.4891</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4915</v>
+        <v>-0.2929</v>
       </c>
       <c r="G12" t="n">
         <v>-1.524</v>
@@ -1390,13 +1390,13 @@
         <v>0.1931</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1988</v>
+        <v>-0.2</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0825</v>
+        <v>-0.1174</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2813</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2856</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.1855</v>
+        <v>-5.0655</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.1553</v>
+        <v>-4.8863</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0302</v>
+        <v>-0.1792</v>
       </c>
       <c r="G13" t="n">
         <v>-2.0185</v>
@@ -1468,13 +1468,13 @@
         <v>1.3515</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1766</v>
+        <v>0.2966</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4142</v>
+        <v>-0.1452</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5907</v>
+        <v>0.4418</v>
       </c>
       <c r="V13" t="n">
         <v>-1.7989</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>15.3189</v>
+        <v>16.1464</v>
       </c>
       <c r="E14" t="n">
-        <v>2.505100000000001</v>
+        <v>3.332699999999997</v>
       </c>
       <c r="F14" t="n">
-        <v>12.8139</v>
+        <v>12.8136</v>
       </c>
       <c r="G14" t="n">
         <v>7.828700000000001</v>
@@ -1522,16 +1522,16 @@
         <v>8.9755</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3506999999999998</v>
+        <v>0.3507000000000002</v>
       </c>
       <c r="L14" t="n">
-        <v>8.624999999999996</v>
+        <v>8.624999999999998</v>
       </c>
       <c r="M14" t="n">
         <v>-1.1469</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.762700000000001</v>
+        <v>-2.7627</v>
       </c>
       <c r="O14" t="n">
         <v>1.6156</v>
@@ -1546,13 +1546,13 @@
         <v>16.4115</v>
       </c>
       <c r="S14" t="n">
-        <v>4.412899999999999</v>
+        <v>5.2405</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.003399999999999959</v>
+        <v>0.8242</v>
       </c>
       <c r="U14" t="n">
-        <v>4.416300000000001</v>
+        <v>4.4162</v>
       </c>
       <c r="V14" t="n">
         <v>-0.7844</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2838</v>
+        <v>4.3594</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3315</v>
+        <v>2.6418</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9522</v>
+        <v>1.7176</v>
       </c>
       <c r="G15" t="n">
         <v>3.3855</v>
@@ -1624,13 +1624,13 @@
         <v>1.5446</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2755</v>
+        <v>-0.1998</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6898</v>
+        <v>-0.3796</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4143</v>
+        <v>0.1798</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3709</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.2338</v>
+        <v>3.2931</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0981</v>
+        <v>2.9947</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1357</v>
+        <v>0.2984</v>
       </c>
       <c r="G16" t="n">
         <v>0.4558</v>
@@ -1702,13 +1702,13 @@
         <v>1.9308</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3973</v>
+        <v>-0.3379</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0555</v>
+        <v>-0.159</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3417</v>
+        <v>-0.179</v>
       </c>
       <c r="V16" t="n">
         <v>2.2098</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.0421</v>
+        <v>1.9676</v>
       </c>
       <c r="E17" t="n">
         <v>0.6851</v>
       </c>
       <c r="F17" t="n">
-        <v>1.357</v>
+        <v>1.2825</v>
       </c>
       <c r="G17" t="n">
         <v>1.5578</v>
@@ -1780,13 +1780,13 @@
         <v>0.1931</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0056</v>
+        <v>-0.0689</v>
       </c>
       <c r="T17" t="n">
         <v>-0.1932</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1988</v>
+        <v>0.1243</v>
       </c>
       <c r="V17" t="n">
         <v>0.2856</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0948</v>
+        <v>-0.1692</v>
       </c>
       <c r="E18" t="n">
         <v>-1.5973</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5026</v>
+        <v>1.4281</v>
       </c>
       <c r="G18" t="n">
         <v>2.7808</v>
@@ -1858,13 +1858,13 @@
         <v>1.3515</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4909</v>
+        <v>-0.5654</v>
       </c>
       <c r="T18" t="n">
         <v>-0.4968</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0059</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="V18" t="n">
         <v>0.1253</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. BARBEITO RUIZ</t>
+          <t>A. GUERRERO PAEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.257</v>
+        <v>-0.3687</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5239</v>
+        <v>-2.4712</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7809</v>
+        <v>2.1026</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4003</v>
+        <v>-1.1963</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0002</v>
+        <v>-0.2763</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4002</v>
+        <v>-0.92</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-1.7675</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>-0.9651</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-0.8024</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4003</v>
+        <v>0.5713</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0002</v>
+        <v>0.6889</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4002</v>
+        <v>-0.1176</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.1585</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.1585</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1434</v>
+        <v>-0.3309</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5239</v>
+        <v>-0.7037</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3806</v>
+        <v>0.3728</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. GUERRERO PAEZ</t>
+          <t>A. BARBEITO RUIZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6997</v>
+        <v>-0.621</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.6781</v>
+        <v>0.1102</v>
       </c>
       <c r="F20" t="n">
-        <v>1.9784</v>
+        <v>-0.7312</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1963</v>
+        <v>-0.4003</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2763</v>
+        <v>-0.0002</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.92</v>
+        <v>-0.4002</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.7675</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9651</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.8024</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5713</v>
+        <v>-0.4003</v>
       </c>
       <c r="N20" t="n">
-        <v>0.6889</v>
+        <v>-0.0002</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1176</v>
+        <v>-0.4002</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1585</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1585</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6619</v>
+        <v>-0.2207</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9106</v>
+        <v>0.1102</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2487</v>
+        <v>-0.3309</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6104</v>
+        <v>-1.1126</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3739</v>
+        <v>-1.0637</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2365</v>
+        <v>-0.0489</v>
       </c>
       <c r="G21" t="n">
         <v>-0.3125</v>
@@ -2092,13 +2092,13 @@
         <v>1.1585</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8771</v>
+        <v>-0.3793</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4966</v>
+        <v>-0.1864</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3805</v>
+        <v>-0.1929</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6138</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0159</v>
+        <v>-2.3662</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4219</v>
+        <v>-0.8356</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.594</v>
+        <v>-1.5306</v>
       </c>
       <c r="G22" t="n">
         <v>-1.8499</v>
@@ -2170,13 +2170,13 @@
         <v>1.3515</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2813</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2756</v>
+        <v>-0.1381</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0058</v>
+        <v>0.0692</v>
       </c>
       <c r="V22" t="n">
         <v>-1.7989</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Í. MATEO CASTAÑO</t>
+          <t>A. MARÍN REYES</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.399</v>
+        <v>-3.2243</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8778</v>
+        <v>-2.5183</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.5213</v>
+        <v>-0.706</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.4031</v>
+        <v>-3.7296</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2132</v>
+        <v>-0.7727000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.6163</v>
+        <v>-2.9569</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-1.37</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.5446</v>
+        <v>-1.2548</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5359</v>
+        <v>-0.1152</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3943</v>
+        <v>-2.3596</v>
       </c>
       <c r="N23" t="n">
-        <v>0.7579</v>
+        <v>0.4821</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.1522</v>
+        <v>-2.8417</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.7723</v>
+        <v>-2.7031</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9308</v>
+        <v>-3.8616</v>
       </c>
       <c r="R23" t="n">
         <v>1.1585</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5352</v>
+        <v>-0.6</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1659</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>0.7010999999999999</v>
+        <v>0.0416</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.7588</v>
+        <v>3.8084</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2277</v>
+        <v>3.3548</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.9865</v>
+        <v>0.4535</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. MARÍN REYES</t>
+          <t>Í. MATEO CASTAÑO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.6505</v>
+        <v>-3.7549</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.6218</v>
+        <v>-1.0846</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0288</v>
+        <v>-2.6703</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.7296</v>
+        <v>-1.4031</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.7727000000000001</v>
+        <v>0.2132</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.9569</v>
+        <v>-1.6163</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.37</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.2548</v>
+        <v>-0.5446</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.1152</v>
+        <v>0.5359</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.3596</v>
+        <v>-1.3943</v>
       </c>
       <c r="N24" t="n">
-        <v>0.4821</v>
+        <v>0.7579</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.8417</v>
+        <v>-2.1522</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.7031</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.8616</v>
+        <v>-1.9308</v>
       </c>
       <c r="R24" t="n">
         <v>1.1585</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0262</v>
+        <v>0.1794</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.745</v>
+        <v>-0.3727</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2812</v>
+        <v>0.5521</v>
       </c>
       <c r="V24" t="n">
-        <v>3.8084</v>
+        <v>-1.7588</v>
       </c>
       <c r="W24" t="n">
-        <v>3.3548</v>
+        <v>1.2277</v>
       </c>
       <c r="X24" t="n">
-        <v>0.4535</v>
+        <v>-2.9865</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A. FORTES SILVA</t>
+          <t>J. OLIVA DOMINGUEZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.465</v>
+        <v>-6.2958</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.8971</v>
+        <v>-4.8811</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.568</v>
+        <v>-1.4147</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.8984</v>
+        <v>-4.2186</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1381</v>
+        <v>-0.4004</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.7603</v>
+        <v>-3.8182</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.263</v>
+        <v>-2.6729</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.3443</v>
+        <v>0.0828</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0814</v>
+        <v>-2.7556</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.6354</v>
+        <v>-1.5458</v>
       </c>
       <c r="N25" t="n">
-        <v>0.2063</v>
+        <v>-0.4832</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.8417</v>
+        <v>-1.0626</v>
       </c>
       <c r="P25" t="n">
-        <v>-3.0892</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.8616</v>
+        <v>-0.9654</v>
       </c>
       <c r="R25" t="n">
         <v>0.7723</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5627</v>
+        <v>-0.6965</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7725</v>
+        <v>-0.5864</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2099</v>
+        <v>-0.1101</v>
       </c>
       <c r="V25" t="n">
-        <v>0.0852</v>
+        <v>-1.1876</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>-0.6565</v>
       </c>
       <c r="X25" t="n">
-        <v>0.0852</v>
+        <v>-0.5311</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>J. OLIVA DOMINGUEZ</t>
+          <t>A. FORTES SILVA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.6861</v>
+        <v>-6.3368</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.9846</v>
+        <v>-4.7937</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.7015</v>
+        <v>-1.5431</v>
       </c>
       <c r="G26" t="n">
-        <v>-4.2186</v>
+        <v>-2.8984</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.4004</v>
+        <v>-0.1381</v>
       </c>
       <c r="I26" t="n">
-        <v>-3.8182</v>
+        <v>-2.7603</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.6729</v>
+        <v>-0.263</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0828</v>
+        <v>-0.3443</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.7556</v>
+        <v>0.0814</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.5458</v>
+        <v>-2.6354</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.4832</v>
+        <v>0.2063</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.0626</v>
+        <v>-2.8417</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.1931</v>
+        <v>-3.0892</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.9654</v>
+        <v>-3.8616</v>
       </c>
       <c r="R26" t="n">
         <v>0.7723</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.0868</v>
+        <v>-0.4344</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.6898</v>
+        <v>-0.6691</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.397</v>
+        <v>0.2347</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.1876</v>
+        <v>0.0852</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.6565</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.5311</v>
+        <v>0.0852</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-15.3187</v>
+        <v>-14.6294</v>
       </c>
       <c r="E27" t="n">
-        <v>-12.8139</v>
+        <v>-12.8137</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.505100000000001</v>
+        <v>-1.815600000000001</v>
       </c>
       <c r="G27" t="n">
         <v>-7.828800000000001</v>
@@ -2560,19 +2560,19 @@
         <v>12.5501</v>
       </c>
       <c r="S27" t="n">
-        <v>-4.4129</v>
+        <v>-3.7234</v>
       </c>
       <c r="T27" t="n">
-        <v>-4.4162</v>
+        <v>-4.4164</v>
       </c>
       <c r="U27" t="n">
-        <v>0.003499999999999837</v>
+        <v>0.6930000000000001</v>
       </c>
       <c r="V27" t="n">
         <v>0.7842999999999998</v>
       </c>
       <c r="W27" t="n">
-        <v>6.8674</v>
+        <v>6.867400000000001</v>
       </c>
       <c r="X27" t="n">
         <v>-6.083</v>
